--- a/output/Data and Chart Outputs/south_southeast_asia_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/south_southeast_asia_power_by_type.xlsx
@@ -168,6 +168,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>India power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -471,6 +472,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Pakistan power generation by type (to Mar/26)</a:t>
             </a:r>
           </a:p>
@@ -774,6 +776,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bangladesh power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -1077,6 +1080,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Sri Lanka power generation by type (to Jun/24)</a:t>
             </a:r>
           </a:p>
@@ -1380,6 +1384,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Thailand power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -1683,6 +1688,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Vietnam power generation by type (to Oct/25)</a:t>
             </a:r>
           </a:p>
@@ -1986,6 +1992,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Philippines power generation by type (to Jun/26)</a:t>
             </a:r>
           </a:p>
@@ -2289,6 +2296,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Malaysia power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -2592,6 +2600,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore power generation by type (to Feb/26)</a:t>
             </a:r>
           </a:p>
@@ -3460,7 +3469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. India: 2021-01 to 2026-05; Pakistan: 2021-01 to 2026-03; Bangladesh: 2021-01 to 2026-05; Sri Lanka: 2021-01 to 2024-06; Thailand: 2021-01 to 2026-04; Vietnam: 2021-01 to 2025-10; Philippines: 2021-01 to 2026-06; Malaysia: 2021-01 to 2026-05; Singapore: 2021-01 to 2026-02. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. India: 2021-01 to 2026-05; Pakistan: 2021-01 to 2026-03; Bangladesh: 2021-01 to 2026-05; Sri Lanka: 2021-01 to 2024-06; Thailand: 2021-01 to 2026-04; Vietnam: 2021-01 to 2025-10; Philippines: 2021-01 to 2026-06; Malaysia: 2021-01 to 2026-05; Singapore: 2021-01 to 2026-02. Ember lags real time by one to several months (it varies by country); each scheduled run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
